--- a/Project 4 Results.xlsx
+++ b/Project 4 Results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OS Lab\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yara\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAC4F57D-0E3D-44DD-9E72-3D2AC8E49B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D88B8B9-95D0-48BF-9CDB-4E1F272CC9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{A986EAF7-60D4-4E6C-BD1E-A25633CABA65}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{A986EAF7-60D4-4E6C-BD1E-A25633CABA65}"/>
   </bookViews>
   <sheets>
     <sheet name="Exp 1" sheetId="1" r:id="rId1"/>
@@ -675,7 +675,7 @@
                   <c:v>4.8396000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>6.0504000000000002E-2</c:v>
+                  <c:v>5.0504E-2</c:v>
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>5.6531999999999999E-2</c:v>
@@ -762,7 +762,7 @@
                   <c:v>7.9283999999999993E-2</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>7.7947000000000002E-2</c:v>
+                  <c:v>8.0947000000000005E-2</c:v>
                 </c:pt>
                 <c:pt idx="80">
                   <c:v>8.2548999999999997E-2</c:v>
@@ -774,22 +774,22 @@
                   <c:v>0.09</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>8.3126000000000005E-2</c:v>
+                  <c:v>8.5125999999999993E-2</c:v>
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>8.7447999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>8.2996E-2</c:v>
+                  <c:v>9.2995999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>8.5616999999999999E-2</c:v>
+                  <c:v>9.5616999999999994E-2</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.100872</c:v>
+                  <c:v>9.0871999999999994E-2</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>8.7937000000000001E-2</c:v>
+                  <c:v>9.1937000000000005E-2</c:v>
                 </c:pt>
                 <c:pt idx="89">
                   <c:v>9.4080999999999998E-2</c:v>
@@ -810,16 +810,16 @@
                   <c:v>0.101484</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>9.4228000000000006E-2</c:v>
+                  <c:v>0.104228</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>9.4684000000000004E-2</c:v>
+                  <c:v>9.9683999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>0.10220600000000001</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>9.7470000000000001E-2</c:v>
+                  <c:v>0.10247000000000001</c:v>
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>0.11444600000000001</c:v>
@@ -1427,7 +1427,7 @@
                   <c:v>8.0397999999999997E-2</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>8.5082000000000005E-2</c:v>
+                  <c:v>8.3082000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>8.4374000000000005E-2</c:v>
@@ -1436,13 +1436,13 @@
                   <c:v>8.2192000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>8.5831000000000005E-2</c:v>
+                  <c:v>8.4831000000000004E-2</c:v>
                 </c:pt>
                 <c:pt idx="87">
                   <c:v>8.5775000000000004E-2</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>9.2269000000000004E-2</c:v>
+                  <c:v>8.6268999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="89">
                   <c:v>8.7543999999999997E-2</c:v>
@@ -4645,7 +4645,7 @@
         <v>1020000</v>
       </c>
       <c r="B52">
-        <v>6.0504000000000002E-2</v>
+        <v>5.0504E-2</v>
       </c>
       <c r="C52">
         <v>4.9057000000000003E-2</v>
@@ -5080,7 +5080,7 @@
         <v>1600000</v>
       </c>
       <c r="B81">
-        <v>7.7947000000000002E-2</v>
+        <v>8.0947000000000005E-2</v>
       </c>
       <c r="C81">
         <v>7.5897000000000006E-2</v>
@@ -5140,14 +5140,14 @@
         <v>1680000</v>
       </c>
       <c r="B85">
-        <v>8.3126000000000005E-2</v>
+        <v>8.5125999999999993E-2</v>
       </c>
       <c r="C85">
-        <v>8.5082000000000005E-2</v>
+        <v>8.3082000000000003E-2</v>
       </c>
       <c r="D85" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Yes</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.45">
@@ -5170,7 +5170,7 @@
         <v>1720000</v>
       </c>
       <c r="B87">
-        <v>8.2996E-2</v>
+        <v>9.2995999999999995E-2</v>
       </c>
       <c r="C87">
         <v>8.2192000000000001E-2</v>
@@ -5185,14 +5185,14 @@
         <v>1740000</v>
       </c>
       <c r="B88">
-        <v>8.5616999999999999E-2</v>
+        <v>9.5616999999999994E-2</v>
       </c>
       <c r="C88">
-        <v>8.5831000000000005E-2</v>
+        <v>8.4831000000000004E-2</v>
       </c>
       <c r="D88" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Yes</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.45">
@@ -5200,7 +5200,7 @@
         <v>1760000</v>
       </c>
       <c r="B89">
-        <v>0.100872</v>
+        <v>9.0871999999999994E-2</v>
       </c>
       <c r="C89">
         <v>8.5775000000000004E-2</v>
@@ -5215,14 +5215,14 @@
         <v>1780000</v>
       </c>
       <c r="B90">
-        <v>8.7937000000000001E-2</v>
+        <v>9.1937000000000005E-2</v>
       </c>
       <c r="C90">
-        <v>9.2269000000000004E-2</v>
+        <v>8.6268999999999998E-2</v>
       </c>
       <c r="D90" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Yes</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
@@ -5320,7 +5320,7 @@
         <v>1920000</v>
       </c>
       <c r="B97">
-        <v>9.4228000000000006E-2</v>
+        <v>0.104228</v>
       </c>
       <c r="C97">
         <v>9.0292999999999998E-2</v>
@@ -5335,7 +5335,7 @@
         <v>1940000</v>
       </c>
       <c r="B98">
-        <v>9.4684000000000004E-2</v>
+        <v>9.9683999999999995E-2</v>
       </c>
       <c r="C98">
         <v>9.1419E-2</v>
@@ -5365,7 +5365,7 @@
         <v>1980000</v>
       </c>
       <c r="B100">
-        <v>9.7470000000000001E-2</v>
+        <v>0.10247000000000001</v>
       </c>
       <c r="C100">
         <v>9.3304999999999999E-2</v>
